--- a/exports/registri_compilati/registro_1EA.xlsx
+++ b/exports/registri_compilati/registro_1EA.xlsx
@@ -82,12 +82,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -597,7 +597,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
           <t>BENAGLIA SIMONE</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -619,9 +619,9 @@
           <t>BORACCI DAVIDE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -631,9 +631,9 @@
           <t>BOSIS FILIPPO</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -643,9 +643,9 @@
           <t>COLOMBI MATTEO</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -655,9 +655,9 @@
           <t>CRISTE GABRIELE</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -703,9 +703,9 @@
           <t>HU MICHELE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -715,9 +715,9 @@
           <t>LOMACCI LORENZO</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -727,9 +727,9 @@
           <t>LUISELLI GIOELE</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -739,9 +739,9 @@
           <t>MAGGIO GABRIEL</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -751,9 +751,9 @@
           <t>MEDOLAGO NICOLO'</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -763,9 +763,9 @@
           <t>MEREGALLI FILIPPO</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -775,9 +775,9 @@
           <t>MICCOLI GABRIELE</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -787,9 +787,9 @@
           <t>PIGNATELLI FABIO</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -799,9 +799,9 @@
           <t>RAVASIO RICCARDO</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -811,9 +811,9 @@
           <t>ROTASPERTI CRISTIAN</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -823,9 +823,9 @@
           <t>SINGH JASKIRAT</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -835,9 +835,9 @@
           <t>TENORIO GUARACHI DAVIDE</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -847,9 +847,9 @@
           <t>TIRONI SIMONE</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -859,9 +859,9 @@
           <t>YAACOUB LORENZO MILAD SALAMA ROMAN</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -871,9 +871,9 @@
           <t>ZIBETTI DIEGO ALESSANDRO</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -883,9 +883,9 @@
           <t>ZINESI KARL</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -895,9 +895,9 @@
           <t>ZUCCLINI SIMONE</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>D</t>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>P</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:00</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>ufficiotecnico@itispaleocapa.it</t>
         </is>
       </c>
     </row>
